--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="456">
   <si>
     <t>Property</t>
   </si>
@@ -561,7 +561,13 @@
     <t>内視鏡を表すモダリティコード”ES”を指定する。複数モダリティを使用した場合には、該当するモダリティコードを並記する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>「インスタンスにおける取得データの種類。」</t>
+  </si>
+  <si>
+    <t>http://dicom.nema.org/medical/dicom/current/output/chtml/part16/sect_CID_29.html</t>
   </si>
   <si>
     <t>.code</t>
@@ -849,10 +855,10 @@
     <t>内視鏡では省略してよい。</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://playbook.radlex.org/playbook/SearchRadlexAction</t>
+    <t>実行された手順のタイプ。</t>
+  </si>
+  <si>
+    <t>http://www.rsna.org/RadLex_Playbook.aspx</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1113,6 +1119,9 @@
   </si>
   <si>
     <t>内視鏡を表すモダリティコード”ES”を指定する。1シリーズ1モダリティで、1つのシリーズの中に複数のモダリティが混在することはない。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>(0008,0060)</t>
@@ -3268,11 +3277,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3308,13 +3319,13 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3322,10 +3333,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3348,16 +3359,16 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3407,7 +3418,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3422,16 +3433,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3439,10 +3450,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3465,16 +3476,16 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3524,7 +3535,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3539,16 +3550,16 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3556,14 +3567,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3582,13 +3593,13 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3603,7 +3614,7 @@
         <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>79</v>
@@ -3639,7 +3650,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3654,16 +3665,16 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>79</v>
@@ -3671,10 +3682,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3697,19 +3708,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3758,7 +3769,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3773,16 +3784,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3790,14 +3801,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3816,16 +3827,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3875,7 +3886,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3893,13 +3904,13 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3907,14 +3918,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3933,16 +3944,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3992,7 +4003,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4010,13 +4021,13 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4024,10 +4035,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4050,19 +4061,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4111,7 +4122,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4129,7 +4140,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4143,14 +4154,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4169,13 +4180,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4226,7 +4237,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4244,10 +4255,10 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>79</v>
@@ -4258,14 +4269,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4284,13 +4295,13 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4341,7 +4352,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4359,10 +4370,10 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
@@ -4373,10 +4384,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4399,16 +4410,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4458,7 +4469,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4473,13 +4484,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -4490,14 +4501,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4516,16 +4527,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4551,11 +4562,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4573,7 +4586,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4588,13 +4601,13 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4605,10 +4618,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4631,19 +4644,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4692,7 +4705,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4707,27 +4720,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4750,16 +4763,16 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4785,11 +4798,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4807,7 +4820,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4822,16 +4835,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4839,10 +4852,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4865,16 +4878,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4924,7 +4937,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4939,27 +4952,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4982,13 +4995,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5039,7 +5052,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5054,10 +5067,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5071,14 +5084,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5097,16 +5110,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5156,7 +5169,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5174,10 +5187,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5188,10 +5201,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5214,13 +5227,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5271,7 +5284,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5289,7 +5302,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5303,10 +5316,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5329,13 +5342,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5386,7 +5399,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5404,7 +5417,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5418,10 +5431,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5450,7 +5463,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5503,7 +5516,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5521,7 +5534,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5535,14 +5548,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5564,10 +5577,10 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -5622,7 +5635,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5654,14 +5667,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5683,16 +5696,16 @@
         <v>92</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5705,7 +5718,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5741,7 +5754,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5759,10 +5772,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5773,14 +5786,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5799,13 +5812,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5820,7 +5833,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5856,7 +5869,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5874,10 +5887,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5888,14 +5901,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5917,13 +5930,13 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5953,7 +5966,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>175</v>
+        <v>353</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -5971,7 +5984,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -5989,10 +6002,10 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6003,14 +6016,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6029,13 +6042,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6050,7 +6063,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6086,7 +6099,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6104,10 +6117,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6118,14 +6131,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6144,13 +6157,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6201,7 +6214,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6219,10 +6232,10 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6233,10 +6246,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6259,19 +6272,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6320,7 +6333,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6338,7 +6351,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6352,14 +6365,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6381,13 +6394,13 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6413,13 +6426,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6437,7 +6450,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6455,10 +6468,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6469,10 +6482,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6498,13 +6511,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6530,31 +6543,31 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6572,10 +6585,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6586,10 +6599,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6612,16 +6625,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6671,7 +6684,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6689,10 +6702,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6703,10 +6716,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6729,16 +6742,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6788,7 +6801,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6806,10 +6819,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6820,14 +6833,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6846,19 +6859,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6907,7 +6920,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6922,13 +6935,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6939,10 +6952,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6965,13 +6978,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7022,7 +7035,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7040,7 +7053,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7054,10 +7067,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7086,7 +7099,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7139,7 +7152,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7157,7 +7170,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7171,14 +7184,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7200,10 +7213,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7258,7 +7271,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7290,10 +7303,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7316,19 +7329,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7353,13 +7366,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>266</v>
+        <v>175</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7377,7 +7390,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7395,7 +7408,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7409,10 +7422,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7435,16 +7448,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7494,7 +7507,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7512,24 +7525,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7552,13 +7565,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7609,7 +7622,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7627,7 +7640,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7641,10 +7654,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7667,13 +7680,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7724,7 +7737,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7742,7 +7755,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7756,10 +7769,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7788,7 +7801,7 @@
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>139</v>
@@ -7841,7 +7854,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7859,7 +7872,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7873,14 +7886,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7902,10 +7915,10 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -7960,7 +7973,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7992,14 +8005,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8021,16 +8034,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8043,7 +8056,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8079,7 +8092,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8097,10 +8110,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8111,14 +8124,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8140,13 +8153,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8172,13 +8185,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>266</v>
+        <v>175</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8196,7 +8209,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8214,10 +8227,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8228,14 +8241,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8254,16 +8267,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8313,7 +8326,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8331,10 +8344,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8345,10 +8358,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8371,16 +8384,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8430,7 +8443,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8448,10 +8461,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="455">
   <si>
     <t>Property</t>
   </si>
@@ -1119,9 +1119,6 @@
   </si>
   <si>
     <t>内視鏡を表すモダリティコード”ES”を指定する。1シリーズ1モダリティで、1つのシリーズの中に複数のモダリティが混在することはない。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>(0008,0060)</t>
@@ -5962,11 +5959,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>353</v>
+        <v>177</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6005,7 +6004,7 @@
         <v>178</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6016,14 +6015,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6045,10 +6044,10 @@
         <v>308</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6063,7 +6062,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6099,7 +6098,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6120,7 +6119,7 @@
         <v>312</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6131,14 +6130,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6160,10 +6159,10 @@
         <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6214,7 +6213,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6235,7 +6234,7 @@
         <v>252</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6246,10 +6245,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6275,16 +6274,16 @@
         <v>235</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6333,7 +6332,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6365,14 +6364,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6394,10 +6393,10 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>267</v>
@@ -6429,11 +6428,11 @@
         <v>286</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6450,7 +6449,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6468,10 +6467,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6482,10 +6481,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6511,10 +6510,10 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>267</v>
@@ -6546,11 +6545,11 @@
         <v>286</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>383</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6567,7 +6566,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6585,10 +6584,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6599,10 +6598,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6625,13 +6624,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>267</v>
@@ -6684,7 +6683,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6702,10 +6701,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6716,10 +6715,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6745,13 +6744,13 @@
         <v>200</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6801,7 +6800,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6822,7 +6821,7 @@
         <v>205</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6833,14 +6832,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6862,16 +6861,16 @@
         <v>315</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>267</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6920,7 +6919,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6935,13 +6934,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>231</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6952,10 +6951,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7067,10 +7066,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7184,10 +7183,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7303,10 +7302,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7332,16 +7331,16 @@
         <v>264</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>267</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7369,11 +7368,11 @@
         <v>175</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7390,7 +7389,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7422,10 +7421,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7448,13 +7447,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>267</v>
@@ -7507,7 +7506,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7525,24 +7524,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>418</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7568,10 +7567,10 @@
         <v>315</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7622,7 +7621,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7640,7 +7639,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7654,10 +7653,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7769,10 +7768,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7886,10 +7885,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8005,14 +8004,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8034,16 +8033,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8056,7 +8055,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8092,7 +8091,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8113,7 +8112,7 @@
         <v>339</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8124,14 +8123,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8153,13 +8152,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8188,11 +8187,11 @@
         <v>175</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8209,7 +8208,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8227,10 +8226,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8241,14 +8240,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8270,13 +8269,13 @@
         <v>243</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8326,7 +8325,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8344,10 +8343,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8358,10 +8357,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8387,13 +8386,13 @@
         <v>308</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8443,7 +8442,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8461,10 +8460,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$57</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="442">
   <si>
     <t>Property</t>
   </si>
@@ -484,13 +481,13 @@
 </t>
   </si>
   <si>
-    <t>DICOM画像検査全体を一意に識別するためのID【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像検査全体を一意に識別するためのID。</t>
-  </si>
-  <si>
-    <t>Study Instance UIDの値を指定する。</t>
+    <t>「全体の研究の識別子」</t>
+  </si>
+  <si>
+    <t>「DICOMスタディインスタンスUIDやアクセッション番号のようなImagingStudyの識別子」</t>
+  </si>
+  <si>
+    <t>「DICOM Study Instance UIDのエンコーディングについては、[Imaging Study Implementation Notes]（imagingstudy.html＃notes）のディスカッションを参照してください。アクセッション番号はACSN識別子タイプを使用する必要があります。」</t>
   </si>
   <si>
     <t>If one or more series elements are present in the ImagingStudy, then there shall be one DICOM Study UID identifier (see [DICOM PS 3.3 C.7.2](http://dicom.nema.org/medical/dicom/current/output/chtml/part03/sect_C.7.2.html).</t>
@@ -511,10 +508,10 @@
     <t>ImagingStudy.status</t>
   </si>
   <si>
-    <t>DICOM画像検査のステータス</t>
-  </si>
-  <si>
-    <t>DICOM画像検査のステータス。</t>
+    <t>"登録済み | 利用可能 | 取消済み | エラーで入力 | 不明" (Tōrokuzumi | Riyō kanō | Torikeshi zumi | Erā de nyūryoku | Fumei)</t>
+  </si>
+  <si>
+    <t>「ImagingStudyの現在の状態。」</t>
   </si>
   <si>
     <t>「不明」は「その他」を表すものではありません-定義された状態の1つが適用される必要があります。「不明」は、制作システムが現在の状態を確信できない場合に使用されます。」</t>
@@ -552,13 +549,10 @@
 </t>
   </si>
   <si>
-    <t>DICOM画像検査で使用された撮影装置（モダリティ）【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像検査で使用された撮影装置（モダリティ）。</t>
-  </si>
-  <si>
-    <t>内視鏡を表すモダリティコード”ES”を指定する。複数モダリティを使用した場合には、該当するモダリティコードを並記する。</t>
+    <t>すべてのシリーズのモダリティは実際の取得モダリティである。</t>
+  </si>
+  <si>
+    <t>「DICOMコンテキストグループ29（値セットOID 1.2.840.10008.6.1.19）にある、実際の取得モダリティであるすべてのシリーズモダリティ値のリスト。」</t>
   </si>
   <si>
     <t>extensible</t>
@@ -582,17 +576,17 @@
     <t>ImagingStudy.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(Patient|Device|Group)
 </t>
   </si>
   <si>
-    <t>DICOM画像検査の対象患者に関する情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像検査の対象患者に関する情報。</t>
-  </si>
-  <si>
-    <t>JP Core Patientリソースを参照する。</t>
+    <t>「誰または何が研究の主題ですか？」(Dare mata wa nani ga kenkyū no shudai desu ka?)</t>
+  </si>
+  <si>
+    <t>画像検査の被写体、通常患者。</t>
+  </si>
+  <si>
+    <t>「QAファントムはデバイスで記録できます。複数の対象（例えば、ネズミなど）はグループで記録できます。」</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -610,17 +604,17 @@
     <t>ImagingStudy.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
-    <t>このDICOM画像検査を実施するきっかけとなった情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>このDICOM画像検査を実施するきっかけとなった情報。</t>
-  </si>
-  <si>
-    <t>JP Core Encounterリソースを参照する。</t>
+    <t>「このイメージング研究に関連する出会い」</t>
+  </si>
+  <si>
+    <t>このImagingStudyが作成される医療イベント（例：患者と医療提供者の相互作用）.</t>
+  </si>
+  <si>
+    <t>これは通常、イベントが発生した出来事の中で発生しますが、公式の出会いの完了前または後に開始されることがありますが、出会いの文脈に関連している場合があります（例：入院前検査）。</t>
   </si>
   <si>
     <t>Event.encounter</t>
@@ -643,10 +637,10 @@
 </t>
   </si>
   <si>
-    <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時</t>
-  </si>
-  <si>
-    <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時。</t>
+    <t>「研究が始まった時」</t>
+  </si>
+  <si>
+    <t>研究が始まった日時。</t>
   </si>
   <si>
     <t>2011-01-01T11:01:20+03:00</t>
@@ -671,13 +665,10 @@
 </t>
   </si>
   <si>
-    <t>他のシステムから依頼されたオーダ情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>他のシステムから依頼されたオーダ情報。</t>
-  </si>
-  <si>
-    <t>通常、依頼元となるServiceRequestリソースを参照する。他のシステムと連携していない場合は参照不要。</t>
+    <t>「リクエストを叶えました」(Rikuesuto wo kanaemashita)</t>
+  </si>
+  <si>
+    <t>この画像検査を実施する結果となった診断依頼のリスト。</t>
   </si>
   <si>
     <t>To support grouped procedures (one imaging study supporting multiple ordered procedures, e.g. chest/abdomen/pelvis CT).</t>
@@ -702,17 +693,14 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
 </t>
   </si>
   <si>
-    <t>依頼医師【詳細参照】</t>
-  </si>
-  <si>
-    <t>依頼医師。</t>
-  </si>
-  <si>
-    <t>ServiceRequestから参照できるため必須ではない。画像についていない情報を無理に生成してreferrerに入力する必要はない。使用する場合には、JP Core Practitionerリソースを参照する。</t>
+    <t>「紹介医」(しょうかいい)</t>
+  </si>
+  <si>
+    <t>「依頼 / 照会している医師。」</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=FLFS].target[classCode=DGIMG, moodCode=RQO].participation[typeCode=AUT].role</t>
@@ -728,13 +716,10 @@
 </t>
   </si>
   <si>
-    <t>画像を診断した医師【詳細参照】</t>
-  </si>
-  <si>
-    <t>画像を診断した医師。</t>
-  </si>
-  <si>
-    <t>通常、読影医。内視鏡では省略してよい。使用する場合には、JP Core Practitionerリソースを参照する。</t>
+    <t>「誰がイメージを解釈したのか？」(Dare ga imeeji o kaishaku shita no ka?)</t>
+  </si>
+  <si>
+    <t>「誰がその研究を読み、画像やその他の内容を解釈したのか。」</t>
   </si>
   <si>
     <t>.participation[typeCode=PRF].role</t>
@@ -753,13 +738,13 @@
 </t>
   </si>
   <si>
-    <t>このDICOM画像検査リソースが存在する位置【詳細参照】</t>
-  </si>
-  <si>
-    <t>このDICOM画像検査リソースが存在する位置。</t>
-  </si>
-  <si>
-    <t>基本的には1つ指定する。</t>
+    <t>学習アクセスエンドポイント (gakushuu akusesu endopointo)</t>
+  </si>
+  <si>
+    <t>研究のアクセス（例：クエリ、ビュー、または取得）を提供するネットワークサービス。DICOMエンドポイントの使用に関する情報については、実装ノートを参照してください。研究レベルエンドポイントは、同じEndpoint.connectionTypeを持つシリーズレベルエンドポイントによって上書きされない限り、研究内の各シリーズに適用されます。</t>
+  </si>
+  <si>
+    <t>典型的なエンドポイントタイプは、DICOM WADO-RSで、RESTful APIを使用してネイティブまたはレンダリング（例：JPG、PNG）形式のDICOMインスタンスを取得するために使用されます。DICOM WADO-URIは同様にネイティブまたはレンダリングインスタンスを取得できますが、HTTPクエリベースのアプローチを使用します。 DICOM QIDO-RSは、実際のインスタンスを取得せずにDICOM情報のRESTfulクエリを許可します。また、IHE Invoke Image Display（IID）は、画像ウェブビューアの標準呼び出しを提供します。</t>
   </si>
   <si>
     <t>Access methods for viewing (e.g., IHE’s IID profile) or retrieving (e.g., DICOM’s WADO-URI and WADO-RS) the study or the study’s series or instances. The study-level baseLocation applies to each series in the study, unless overridden in series by a series-level baseLocation of the same type.</t>
@@ -779,10 +764,10 @@
 </t>
   </si>
   <si>
-    <t>このDICOM画像検査に含まれるシリーズ数</t>
-  </si>
-  <si>
-    <t>このDICOM画像検査に含まれるシリーズ数。</t>
+    <t>"勉強に関連するシリーズの数" (Benkyou ni kanren suru shirizu no kazu)</t>
+  </si>
+  <si>
+    <t>研究のシリーズ数。与えられたこの値は、リソースの可用性、セキュリティ、またはその他の要因により、このリソースが含むシリーズ要素の数よりも大きくなる場合があります。シリーズ要素が存在する場合は、この要素が存在する必要があります。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target[classCode=OBSSER, moodCode=EVN].repeatNumber</t>
@@ -798,10 +783,10 @@
 </t>
   </si>
   <si>
-    <t>このDICOM画像検査に含まれるイメージ（インスタンス）の数</t>
-  </si>
-  <si>
-    <t>このDICOM画像検査に含まれるイメージ（インスタンス）の数。</t>
+    <t>研究に関連するインスタンスの数 (Kenkyū ni kanren suru insutansu no kazu)</t>
+  </si>
+  <si>
+    <t>研究内のSOPインスタンスの数。提供される値は、リソースの可用性、セキュリティ、またはその他の要因により、このリソースが含むインスタンス要素の数よりも大きくなる場合があります。この要素は、任意のインスタンス要素が存在する場合に存在する必要があります。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target[classCode=DGIMG, moodCode=EVN].repeatNumber</t>
@@ -813,17 +798,14 @@
     <t>ImagingStudy.procedureReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
+    <t xml:space="preserve">Reference(Procedure)
 </t>
   </si>
   <si>
-    <t>実施された処置に関する情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>実施された処置に関する情報。</t>
-  </si>
-  <si>
-    <t>内視鏡では省略してよい。使用する場合には、JP Core Procedureを参照する。</t>
+    <t>実行された手順の参照 (Jikkou sareta shun no sanshou)</t>
+  </si>
+  <si>
+    <t>このImagingStudyが一部であった手順。</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -846,13 +828,10 @@
 </t>
   </si>
   <si>
-    <t>実施された処置を表すコード【詳細参照】</t>
-  </si>
-  <si>
-    <t>実施された処置を表すコード。</t>
-  </si>
-  <si>
-    <t>内視鏡では省略してよい。</t>
+    <t>実行された手順コード (Jikkō sa reta tejun kōdo)</t>
+  </si>
+  <si>
+    <t>"実行された手順タイプのコード。"</t>
   </si>
   <si>
     <t>実行された手順のタイプ。</t>
@@ -867,17 +846,14 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
-    <t>DICOM画像検査が実施された場所【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像検査が実施された場所。</t>
-  </si>
-  <si>
-    <t>使用する場合には、JP Core Locationリソースを参照する。</t>
+    <t>「ImagingStudyが発生した場所」</t>
+  </si>
+  <si>
+    <t>「ImagingStudyが行われた主要な物理的場所。」</t>
   </si>
   <si>
     <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
@@ -901,19 +877,19 @@
     <t>ImagingStudy.reasonCode</t>
   </si>
   <si>
-    <t>DICOM画像検査が依頼された理由を表す1つ以上のコード【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像検査が依頼された理由を表す1つ以上のコード。</t>
-  </si>
-  <si>
-    <t>JED (Japan Endoscopy Database) Projectで定義されている検査種別については、JED基本情報用語の”検査目的”、”治療目的”のコードを使用することを強く推奨する。</t>
+    <t>「研究が依頼された理由は何ですか？」(Kenkyū ga irai sareta riyū wa nan desu ka?)</t>
+  </si>
+  <si>
+    <t>「なぜイメージングスタディが依頼されたかを示す臨床状態の説明。」</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ReasonCodesJed_VS</t>
+    <t>研究の理由。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -931,17 +907,14 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Endoscopy)
+    <t xml:space="preserve">Reference(Condition|Observation|Media|DiagnosticReport|DocumentReference)
 </t>
   </si>
   <si>
-    <t>DICOM画像検査の実施理由に関する情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像検査の実施理由に関する情報。</t>
-  </si>
-  <si>
-    <t>使用する場合には、JP Core DiagnosticReport Endoscopyリソースを参照する。</t>
+    <t>なぜ勉強が行われたのですか？ (Naze benkyou ga okonawareta no desu ka?)</t>
+  </si>
+  <si>
+    <t>この研究を正当化する存在を示す別の資源を示します。</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -960,10 +933,10 @@
 </t>
   </si>
   <si>
-    <t>description要素に関するコメント</t>
-  </si>
-  <si>
-    <t>description要素に関するコメント。</t>
+    <t>ユーザー定義のコメント (yūzā teigi no komento)</t>
+  </si>
+  <si>
+    <t>DICOMの推奨マッピングに従い、この要素は「Study Description attribute (0008,1030)」から派生しています。画像検査に関する観察や所見は、別のリソース（「Observation」など）に記録するべきで、この要素には記録しないでください。</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -983,13 +956,10 @@
 </t>
   </si>
   <si>
-    <t>DICOM画像検査に関する記述【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像検査に関する記述。</t>
-  </si>
-  <si>
-    <t>JAHIS 内視鏡DICOM画像データ規約の(0008,1030)の記載例に合わせ、検査種別を記載することを推奨する。</t>
+    <t>"Institution-generated description" would be translated as "施設生成の説明 (shisetsu seisei no setsumei)."</t>
+  </si>
+  <si>
+    <t>研究の画像管理者の説明。機関が作成した研究の説明または分類（コンポーネント）の実施。</t>
   </si>
   <si>
     <t>.text</t>
@@ -1005,10 +975,10 @@
 </t>
   </si>
   <si>
-    <t>DICOM画像検査に含まれるシリーズ（大まかな画像のグループ）</t>
-  </si>
-  <si>
-    <t>DICOM画像検査に含まれるシリーズ（大まかな画像のグループ）。</t>
+    <t>それぞれの研究には、1つ以上のインスタンスのシリーズがあります。</t>
+  </si>
+  <si>
+    <t>それぞれの研究には、1つ以上の画像シリーズや他のコンテンツがあります。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=OBSSER, moodCode=EVN]</t>
@@ -1062,13 +1032,13 @@
 </t>
   </si>
   <si>
-    <t>シリーズを一意に識別するためのUID【詳細参照】</t>
-  </si>
-  <si>
-    <t>シリーズを一意に識別するためのUID。</t>
-  </si>
-  <si>
-    <t>Series Instance UID (0020,000E) の値を指定する。</t>
+    <t>「シリーズの DICOM シリーズ・インスタンス UID」</t>
+  </si>
+  <si>
+    <t>シリーズのDICOMシリーズインスタンスUID。</t>
+  </si>
+  <si>
+    <t>「[DICOM PS3.3 C.7.3]を参照してください。(http://dicom.nema.org/medical/dicom/current/output/chtml/part03/sect_C.7.3.html)」</t>
   </si>
   <si>
     <t>DICOM Series Instance UID.</t>
@@ -1090,10 +1060,10 @@
 </t>
   </si>
   <si>
-    <t>Series Instance UIDとは別に、ユーザー（または装置）が自由に決められるシリーズ番号</t>
-  </si>
-  <si>
-    <t>Series Instance UIDとは別に、ユーザー（または装置）が自由に決められるシリーズ番号。</t>
+    <t>このシリーズの数字識別子 (Kono shirīzu no suji shikibetsu-shi)</t>
+  </si>
+  <si>
+    <t>「このシリーズの数値識別子」(Kono shirīzu no suuchi shikibetsushi)</t>
   </si>
   <si>
     <t>3</t>
@@ -1112,13 +1082,10 @@
 </t>
   </si>
   <si>
-    <t>このシリーズが取得された撮影装置（モダリティ）【詳細参照】</t>
-  </si>
-  <si>
-    <t>このシリーズが取得された撮影装置（モダリティ）。</t>
-  </si>
-  <si>
-    <t>内視鏡を表すモダリティコード”ES”を指定する。1シリーズ1モダリティで、1つのシリーズの中に複数のモダリティが混在することはない。</t>
+    <t>"シリーズ内のインスタンスのモダリティ" (Shirīzu-nai no insutansu no modariti)</t>
+  </si>
+  <si>
+    <t>このシリーズの連続性のモダリティ。</t>
   </si>
   <si>
     <t>(0008,0060)</t>
@@ -1131,10 +1098,10 @@
 </t>
   </si>
   <si>
-    <t>このシリーズに関する記述</t>
-  </si>
-  <si>
-    <t>このシリーズに関する記述。</t>
+    <t>「シリーズの要約文（簡潔かつわかりやすい人間向け）」</t>
+  </si>
+  <si>
+    <t>「シリーズの説明。」</t>
   </si>
   <si>
     <t>CT Surview 180</t>
@@ -1150,10 +1117,10 @@
 </t>
   </si>
   <si>
-    <t>このシリーズに含まれる画像枚数</t>
-  </si>
-  <si>
-    <t>このシリーズに含まれる画像枚数。</t>
+    <t>"シリーズ関連インスタンスの数" (Shirīzu kanren insutansu no kazu)</t>
+  </si>
+  <si>
+    <t>研究中のSOPインスタンスの数。与えられた値が、リソースの利用可能性、セキュリティ、またはその他の要因により、このリソースに含まれるインスタンス要素の数よりも大きくなる場合があります。この要素は、インスタンス要素が存在する場合にのみ存在する必要があります。</t>
   </si>
   <si>
     <t>(0020,1209)</t>
@@ -1162,10 +1129,10 @@
     <t>ImagingStudy.series.endpoint</t>
   </si>
   <si>
-    <t>このシリーズのリソースが存在する位置</t>
-  </si>
-  <si>
-    <t>このシリーズのリソースが存在する位置。</t>
+    <t>シリーズアクセスエンドポイント</t>
+  </si>
+  <si>
+    <t>このシリーズにアクセスするためのネットワークサービス（クエリ、ビュー、または取得など）を提供しています。DICOMエンドポイントの使用方法に関する情報については、実装ノートを参照してください。シリーズレベルのエンドポイントが存在する場合、同じEndpoint.connectionTypeを持つスタディレベルのエンドポイントよりも優先されます。</t>
   </si>
   <si>
     <t>典型的なエンドポイントタイプには、レストフルAPIを使用してネイティブまたはレンダリング（例：JPG、PNG）形式のDICOMインスタンスを取得するために使用されるDICOM WADO-RSが含まれ、HTTPクエリベースのアプローチを使用して同様のネイティブまたはレンダリングインスタンスを取得することができるDICOM WADO-URIが含まれ、DICOM情報のRESTfulクエリを可能にするDICOM QIDO-RSが含まれます。</t>
@@ -1181,10 +1148,10 @@
 </t>
   </si>
   <si>
-    <t>このシリーズの対象となる解剖学的部位【詳細参照】</t>
-  </si>
-  <si>
-    <t>このシリーズの対象となる解剖学的部位。</t>
+    <t>検査された身体部位 (Kensa sareta karada bui)</t>
+  </si>
+  <si>
+    <t>調べた解剖学的構造。DICOMパート16附属書L（http://dicom.nema.org/medical/dicom/current/output/chtml/part16/chapter_L.html）を参照して、DICOMからSNOMED-CTのマッピングを確認してください。bodySiteには、撮影された身体部位の側方性を示す場合がありますが、その場合、ImagingStudy.series.lateralityの内容と一致する必要があります。</t>
   </si>
   <si>
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
@@ -1202,10 +1169,10 @@
     <t>ImagingStudy.series.laterality</t>
   </si>
   <si>
-    <t>解剖学的部位の左右【詳細参照】</t>
-  </si>
-  <si>
-    <t>解剖学的部位の左右。</t>
+    <t>「体の部位の左右」(Karada no bubun no sayū)</t>
+  </si>
+  <si>
+    <t>検査される（おそらくペアリングされた）解剖学的構造物の側性。例えば、左膝、両側の肺、または非ペアの腹部。もしあれば、ImagingStudy.series.bodySiteで示された任意の側性情報と一致する必要があります。</t>
   </si>
   <si>
     <t>「適用される部位の側性を示すコード（左側、右側など）」</t>
@@ -1224,10 +1191,10 @@
 </t>
   </si>
   <si>
-    <t>このシリーズの検体に関する情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>このシリーズの検体に関する情報。</t>
+    <t>「標本の画像化」(Hyōhon no gazōka)</t>
+  </si>
+  <si>
+    <t>生検の全スライドイメージングのために撮影された試料。</t>
   </si>
   <si>
     <t>Role[classCode=SPEC]</t>
@@ -1239,13 +1206,10 @@
     <t>ImagingStudy.series.started</t>
   </si>
   <si>
-    <t>このシリーズの開始日時【詳細参照】</t>
-  </si>
-  <si>
-    <t>このシリーズの開始日時。</t>
-  </si>
-  <si>
-    <t>Series Date (0008,0021)、およびSeries Time (0008,0031)（いずれもType3）に値が入っていれば、その値を指定する。</t>
+    <t>「シリーズが始まったとき」</t>
+  </si>
+  <si>
+    <t>シリーズが開始された日付と時間。</t>
   </si>
   <si>
     <t>(0008,0021) + (0008,0031)</t>
@@ -1258,10 +1222,13 @@
 OperatorName</t>
   </si>
   <si>
-    <t>このシリーズの実施医【詳細参照】</t>
-  </si>
-  <si>
-    <t>このシリーズの実施医。</t>
+    <t>"シリーズを演奏したのは誰ですか。" (Shirīzu o ensō shita no wa dare desu ka.)</t>
+  </si>
+  <si>
+    <t>「シリーズを行った人またはものと、彼らがどのように関わっていたかを示しています。」</t>
+  </si>
+  <si>
+    <t>シリーズを実行した人が分かっていない場合、彼らの組織を記録することができます。患者または関係者がパフォーマーになることがあります。例:患者キャプチャイメージの場合。</t>
   </si>
   <si>
     <t>The performer is recorded at the series level, since each series in a study may be performed by a different performer, at different times, and using different devices. A series may be performed by multiple performers.</t>
@@ -1285,10 +1252,10 @@
     <t>ImagingStudy.series.performer.function</t>
   </si>
   <si>
-    <t>このシリーズの実施医の役割【詳細参照】</t>
-  </si>
-  <si>
-    <t>このシリーズの実施医の役割。</t>
+    <t>「パフォーマンスの種類」(Pafōmansu no shurui)</t>
+  </si>
+  <si>
+    <t>"俳優のシリーズへの参加のタイプを区別する。"</t>
   </si>
   <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
@@ -1307,10 +1274,7 @@
 </t>
   </si>
   <si>
-    <t>このシリーズの撮影者、もしくは組織【詳細参照】</t>
-  </si>
-  <si>
-    <t>このシリーズの撮影者、もしくは組織。</t>
+    <t>「シリーズを行った人または物を示す。」</t>
   </si>
   <si>
     <t>.participation[typeCode=PRF].role[scoper.determinerCode=INSTANCE]</t>
@@ -1325,10 +1289,10 @@
     <t>ImagingStudy.series.instance</t>
   </si>
   <si>
-    <t>シリーズに含まれるインスタンス（画像）単位の情報</t>
-  </si>
-  <si>
-    <t>シリーズに含まれるインスタンス（画像）単位の情報。</t>
+    <t>「シリーズからの単一のSOPインスタンス」</t>
+  </si>
+  <si>
+    <t>シリーズ内の単一のSOPインスタンス、例えばイメージまたはプレゼンテーションステート。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=DGIMG, moodCode=EVN]</t>
@@ -1350,13 +1314,13 @@
 </t>
   </si>
   <si>
-    <t>インスタンス（画像）のユニークID【詳細参照】</t>
-  </si>
-  <si>
-    <t>インスタンス（画像）のユニークID。</t>
-  </si>
-  <si>
-    <t>SOP Instance UID (0008,0018) に入力されている値を指定する。</t>
+    <t>DICOM SOPインスタンスUID</t>
+  </si>
+  <si>
+    <t>この画像または他のDICOMコンテンツのDICOM SOPインスタンスUID。</t>
+  </si>
+  <si>
+    <t>[DICOM PS3.3 C.12.1](http://dicom.nema.org/medical/dicom/current/output/chtml/part03/sect_C.12.html#sect_C.12.1)を見てください。</t>
   </si>
   <si>
     <t>DICOM SOP Instance UID.</t>
@@ -1375,15 +1339,10 @@
 </t>
   </si>
   <si>
-    <t>SOPクラスUID【詳細参照】</t>
-  </si>
-  <si>
-    <t>SOPクラスUID。</t>
-  </si>
-  <si>
-    <t>内視鏡では、主に以下の値が指定される。  
-　VL Endoscopic Image Storage:1.2.840.10008.5.1.4.1.1.77.1.1  
-　Secondary Capture Image Storage:1.2.840.10008.5.1.4.1.1.7</t>
+    <t>DICOMクラスタイプ</t>
+  </si>
+  <si>
+    <t>DICOMインスタンスのタイプ。</t>
   </si>
   <si>
     <t>インスタンスのSOPクラス。</t>
@@ -1405,13 +1364,10 @@
 </t>
   </si>
   <si>
-    <t>SOP Instance UIDとは別に、ユーザー（または装置）が自由に決められるインスタンス（画像）ごとの番号【詳細参照】</t>
-  </si>
-  <si>
-    <t>SOP Instance UIDとは別に、ユーザー（または装置）が自由に決められるインスタンス（画像）ごとの番号。</t>
-  </si>
-  <si>
-    <t>Instance Number (0020,0013) に値が入っていた場合は、その値を指定する。</t>
+    <t>このシリーズにおけるこのインスタンスの番号</t>
+  </si>
+  <si>
+    <t>シリーズ内のインスタンスの数。 (Shirīzu-nai no insutansu no kazu.)</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP, source[classCode=OBSSER, moodCode=EVN]].sequenceNumber</t>
@@ -1423,13 +1379,13 @@
     <t>ImagingStudy.series.instance.title</t>
   </si>
   <si>
-    <t>画像に関する説明【詳細参照】</t>
-  </si>
-  <si>
-    <t>画像に関する説明。</t>
-  </si>
-  <si>
-    <t>部門システム側で説明を付ける場合は、その説明を指定してもよい。</t>
+    <t>"インスタンスの説明" (Insutansu no setsumei)</t>
+  </si>
+  <si>
+    <t>インスタンスの説明。</t>
+  </si>
+  <si>
+    <t>特に、SR、プレゼンテーションステート、値マッピングなどの後継分析オブジェクトに関しては。</t>
   </si>
   <si>
     <t>.title</t>
@@ -1564,21 +1520,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1924,7 +1865,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2039,7 +1980,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2156,7 +2097,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2271,7 +2212,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -2388,7 +2329,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2505,7 +2446,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2622,7 +2563,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2739,7 +2680,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2856,7 +2797,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -2975,7 +2916,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -2994,7 +2935,7 @@
         <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>79</v>
@@ -3094,7 +3035,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -3211,7 +3152,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>169</v>
       </c>
@@ -3247,9 +3188,7 @@
       <c r="M13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>79</v>
@@ -3274,13 +3213,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3316,24 +3255,24 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AO13" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3347,7 +3286,7 @@
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>79</v>
@@ -3356,16 +3295,16 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3415,7 +3354,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3430,27 +3369,27 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AO14" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3473,16 +3412,16 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3532,7 +3471,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3547,31 +3486,31 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AO15" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>198</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3590,13 +3529,13 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3611,7 +3550,7 @@
         <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>79</v>
@@ -3647,7 +3586,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3662,27 +3601,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AO16" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
-      <c r="A17" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3705,19 +3644,17 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" s="2"/>
+      <c r="O17" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3766,7 +3703,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3781,31 +3718,31 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN17" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" hidden="true">
-      <c r="A18" t="s" s="2">
-        <v>218</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3824,17 +3761,15 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -3883,7 +3818,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3901,28 +3836,28 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3941,17 +3876,15 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4000,7 +3933,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4018,24 +3951,24 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4058,19 +3991,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4119,7 +4052,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4137,7 +4070,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4149,16 +4082,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4177,13 +4110,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4234,7 +4167,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4252,10 +4185,10 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>79</v>
@@ -4264,16 +4197,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4292,13 +4225,13 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4349,7 +4282,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4367,10 +4300,10 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
@@ -4379,12 +4312,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4407,17 +4340,15 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4466,7 +4397,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4481,13 +4412,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -4496,16 +4427,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4524,17 +4455,15 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4559,13 +4488,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4583,7 +4512,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4598,13 +4527,13 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4613,12 +4542,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4641,19 +4570,17 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4702,7 +4629,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4717,27 +4644,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4760,17 +4687,15 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4795,11 +4720,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4817,7 +4744,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4832,27 +4759,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4875,17 +4802,15 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4934,7 +4859,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4949,27 +4874,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>299</v>
-      </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4992,13 +4917,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5049,7 +4974,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5064,10 +4989,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5079,16 +5004,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5107,17 +5032,15 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5166,7 +5089,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5184,10 +5107,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5196,12 +5119,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5224,13 +5147,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5281,7 +5204,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5299,7 +5222,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5311,12 +5234,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5339,13 +5262,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5396,7 +5319,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5414,7 +5337,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5426,12 +5349,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5460,7 +5383,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5513,7 +5436,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5531,7 +5454,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5543,16 +5466,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5574,10 +5497,10 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -5632,7 +5555,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5662,16 +5585,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5693,16 +5616,16 @@
         <v>92</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5715,7 +5638,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5751,7 +5674,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5769,10 +5692,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5781,16 +5704,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5809,13 +5732,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5830,7 +5753,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5866,7 +5789,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5884,10 +5807,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5896,16 +5819,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5915,7 +5838,7 @@
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
@@ -5927,14 +5850,12 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5959,14 +5880,14 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y36" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y36" t="s" s="2">
+      <c r="Z36" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
       </c>
@@ -5983,7 +5904,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -6001,10 +5922,10 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6013,16 +5934,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6041,13 +5962,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6062,7 +5983,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6098,7 +6019,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6116,10 +6037,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6128,16 +6049,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6156,13 +6077,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6213,7 +6134,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6231,10 +6152,10 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6243,12 +6164,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6271,19 +6192,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6332,7 +6253,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6350,7 +6271,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6362,16 +6283,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6393,14 +6314,12 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6425,13 +6344,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6449,7 +6368,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6467,10 +6386,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6479,12 +6398,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6510,14 +6429,12 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6542,13 +6459,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6566,7 +6483,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6584,10 +6501,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6596,12 +6513,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6624,17 +6541,15 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6683,7 +6598,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6701,10 +6616,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6713,12 +6628,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6741,17 +6656,15 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6800,7 +6713,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6818,10 +6731,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6830,16 +6743,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6858,19 +6771,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>267</v>
+        <v>388</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6919,7 +6832,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6934,13 +6847,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6949,12 +6862,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6977,13 +6890,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7034,7 +6947,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7052,7 +6965,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7064,12 +6977,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7098,7 +7011,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7151,7 +7064,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7169,7 +7082,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7181,16 +7094,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7212,10 +7125,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7270,7 +7183,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7300,12 +7213,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7328,19 +7241,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7365,13 +7276,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7389,7 +7300,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7407,7 +7318,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7419,12 +7330,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7447,17 +7358,15 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7506,7 +7415,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7524,24 +7433,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7564,13 +7473,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7621,7 +7530,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7639,7 +7548,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7651,12 +7560,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7679,13 +7588,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7736,7 +7645,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7754,7 +7663,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7766,12 +7675,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7800,7 +7709,7 @@
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>139</v>
@@ -7853,7 +7762,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7871,7 +7780,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7883,16 +7792,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7914,10 +7823,10 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -7972,7 +7881,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8002,16 +7911,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8021,7 +7930,7 @@
         <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>79</v>
@@ -8033,16 +7942,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8055,7 +7964,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8091,7 +8000,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8109,10 +8018,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8121,16 +8030,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8140,7 +8049,7 @@
         <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>79</v>
@@ -8152,14 +8061,12 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8184,13 +8091,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8208,7 +8115,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8226,10 +8133,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8238,16 +8145,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8266,17 +8173,15 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8325,7 +8230,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8343,10 +8248,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8355,12 +8260,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8383,16 +8288,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8442,7 +8347,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8460,10 +8365,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
@@ -8473,24 +8378,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO57">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>